--- a/employee_incident_report_forms/035_workplace_safety_incident_discharge_form--employee_incident_report_forms.xlsx
+++ b/employee_incident_report_forms/035_workplace_safety_incident_discharge_form--employee_incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,8 +1171,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Minor'}</t>
+          <t>Minor</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'serious'}</t>
+          <t>serious</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Serious'}</t>
+          <t>Serious</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'near_miss'}</t>
+          <t>near_miss</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Near Miss'}</t>
+          <t>Near Miss</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'actual_harm'}</t>
+          <t>actual_harm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Actual Harm'}</t>
+          <t>Actual Harm</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'injury'}</t>
+          <t>injury</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Injury'}</t>
+          <t>Injury</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'slip,_trip,_and_fall'}</t>
+          <t>slip,_trip,_and_fall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Slip, Trip, and Fall'}</t>
+          <t>Slip, Trip, and Fall</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'equipment_related'}</t>
+          <t>equipment_related</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Equipment Related'}</t>
+          <t>Equipment Related</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'office'}</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Office'}</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
